--- a/engine/egch_study/EGCH_Valuation_Model_05092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_05092026.xlsx
@@ -2657,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2878,16 +2878,16 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Country risk priced off the sovereign's traded default swap</t>
+          <t>A 10% ad-valorem export duty charged on every export tonne, for ever</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Priced off the sovereign's credit rating instead, which is the wider of the two spreads and gives a cost of capital 113 basis points higher</t>
+          <t>No duty at all (6.7226) or half the rate (5.3811)</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>2.509861939402812</v>
+        <v>6.722645205388227</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2897,16 +2897,16 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>A cost of capital that glides from its spot build to a terminal rate made from its own long-run components</t>
+          <t>The new complex's granulated ammonium nitrate priced at a typed US$280/t, the weakest-sourced input in a 304-input register</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>One flat spot rate applied to every explicit year and to the perpetuity</t>
+          <t>Priced at the SAME PRODUCT'S OWN DISCLOSED REALISED PRICE — EGP 20,000/t from note 20, which is US$408.16/t at this model's FY2024/25 rate of 49.00 (4.5269)</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1.437646331702388</v>
+        <v>4.526864429847856</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2916,16 +2916,16 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Terminal growth at the central bank's medium-term inflation target</t>
+          <t>Country risk priced off the sovereign's traded default swap</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Two percentage points below it, which is negative real maintenance growth</t>
+          <t>Priced off the sovereign's credit rating instead, which is the wider of the two spreads and gives a cost of capital 113 basis points higher</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>2.448134918245878</v>
+        <v>2.509861939402812</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2935,16 +2935,16 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 24.4% in year one gliding to 13.9% at the terminal</t>
+          <t>A cost of capital that glides from its spot build to a terminal rate made from its own long-run components</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Every leg floored at the 23.00% sovereign ten-year yield — the company's own facilities print no spread above the policy rate, so no spread is added</t>
+          <t>One flat spot rate applied to every explicit year and to the perpetuity</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>2.89382889923321</v>
+        <v>1.437646331702388</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2954,16 +2954,16 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Beta from the five-year weekly regression of the share against the published EGX30 index</t>
+          <t>Terminal growth at the central bank's medium-term inflation target</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>The lower bound of that regression's own 90% confidence interval</t>
+          <t>Two percentage points below it, which is negative real maintenance growth</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>5.783551427853116</v>
+        <v>2.448134918245878</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2973,16 +2973,16 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Gas at the realised price the company's own loss disclosure implies</t>
+          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 24.4% in year one gliding to 13.9% at the terminal</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>The contract formula price in the operating agreement, which is higher</t>
+          <t>Every leg floored at the 23.00% sovereign ten-year yield — the company's own facilities print no spread above the policy rate, so no spread is added</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>1.32686188934534</v>
+        <v>2.89382889923321</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -2992,16 +2992,16 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>The new complex earning at half its derived nameplate in the terminal year</t>
+          <t>Beta from the five-year weekly regression of the share against the published EGX30 index</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Seventy per cent, which is what a well-run nitrate line achieves</t>
+          <t>The lower bound of that regression's own 90% confidence interval</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>4.465410827653877</v>
+        <v>5.783551427853116</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -3011,16 +3011,16 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure at the company's own observed pre-project rate of 1.12% of revenue</t>
+          <t>Gas at the realised price the company's own loss disclosure implies</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Replacement-rate maintenance: gross fixed assets at the disclosed 3.95% machinery depreciation rate, or 6.11% of revenue</t>
+          <t>The contract formula price in the operating agreement, which is higher</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>3.131128827595877</v>
+        <v>1.32686188934534</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -3030,16 +3030,16 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Capital maintenance charged at what replacing the plant costs today, on the 4.45-year average age the accounts MEASURE — accumulated depreciation over the year's own charge</t>
+          <t>The new complex earning at half its derived nameplate in the terminal year</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Half the 22.1-year life the same accounts imply, 11.04 years, which is what has to be assumed where a company does not disclose enough to measure it</t>
+          <t>Seventy per cent, which is what a well-run nitrate line achieves</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>1.819746729021884</v>
+        <v>4.465410827653877</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3049,16 +3049,16 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Gas consumption at 1,292 cubic metres a tonne of ammonia — the rate implied by allocating three quarters of the single disclosed materials line to gas, which carries the plant's disclosed losses as well as its standard usage</t>
+          <t>Maintenance capital expenditure at the company's own observed pre-project rate of 1.12% of revenue</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>The auditor's own disclosed STANDARD rate of 1,200 cubic metres a tonne, which is what the plant consumes when it runs to specification and excludes the losses</t>
+          <t>Replacement-rate maintenance: gross fixed assets at the disclosed 3.95% machinery depreciation rate, or 6.11% of revenue</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>4.88445528574309</v>
+        <v>3.131128827595877</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3068,25 +3068,63 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Project spending anchored on the observed run rate: the nine-month actual extended to a full year</t>
+          <t>Capital maintenance charged at what replacing the plant costs today, on the 4.45-year average age the accounts MEASURE — accumulated depreciation over the year's own charge</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>The faster profile the first issue of this study used, opening at EGP 3,000m</t>
+          <t>Half the 22.1-year life the same accounts imply, 11.04 years, which is what has to be assumed where a company does not disclose enough to measure it</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>3.832876428749209</v>
+        <v>1.819746729021884</v>
       </c>
       <c r="D27" s="11">
         <f>C27-$D$15</f>
         <v/>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29" ht="39" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Gas consumption at 1,292 cubic metres a tonne of ammonia — the rate implied by allocating three quarters of the single disclosed materials line to gas, which carries the plant's disclosed losses as well as its standard usage</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>The auditor's own disclosed STANDARD rate of 1,200 cubic metres a tonne, which is what the plant consumes when it runs to specification and excludes the losses</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>4.88445528574309</v>
+      </c>
+      <c r="D28" s="11">
+        <f>C28-$D$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Project spending anchored on the observed run rate: the nine-month actual extended to a full year</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>The faster profile the first issue of this study used, opening at EGP 3,000m</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>3.832876428749209</v>
+      </c>
+      <c r="D29" s="11">
+        <f>C29-$D$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Each row is a complete re-run of the model through the same case machinery with one component moved and everything else held. Column C is pasted class 3 and DOES NOT REDRAW; column D is a formula against the published answer so the gap can never drift from the values beside it.</t>
         </is>
@@ -5209,7 +5247,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1">
+    <row r="50" ht="84" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Export duty</t>
@@ -5225,7 +5263,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>2026 replacement of the shortfall levy with an ad-valorem duty tied to the global price</t>
+          <t>Decree No. 258 of 2026 of the Minister of Investment and Foreign Trade, published in the Official Gazette on 25 June 2026 — 10% ad valorem on the FOB invoice value of nitrogen fertiliser exports, the invoice certified by the Chamber of Chemical Industries. It replaced a temporary US$90/t duty imposed in May 2026 for three months; the 10% carries no stated expiry. Pure ammonium nitrate above 34.2% nitrogen and free zone shipments are exempt — urea is neither. Read from two independent reports of the instrument rather than the Gazette text, which is the remaining gap in this citation</t>
         </is>
       </c>
     </row>
